--- a/livrables/passages_niveau_par_bande.xlsx
+++ b/livrables/passages_niveau_par_bande.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="passages_niveau_par_bande" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'passages_niveau_par_bande'!$A$1:$D$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'passages_niveau_par_bande'!$A$1:$D$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,10 +427,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>72</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>243</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>179</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>471</v>
+        <v>426</v>
       </c>
     </row>
     <row r="22">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>53</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="34">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="38">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>136</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>695</v>
+        <v>672</v>
       </c>
     </row>
     <row r="42">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45">
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>233</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49">
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>138</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="54">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="58">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>137</v>
+        <v>157</v>
       </c>
     </row>
     <row r="61">
@@ -1655,11 +1655,811 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>754</v>
+        <v>740</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MTL-QC</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>≤153</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MTL-QC</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>154-177</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>MTL-QC</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>178-201</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>MTL-QC</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>&gt;201</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MTL-Ott</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>≤153</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MTL-Ott</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>154-177</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MTL-Ott</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>178-201</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MTL-Ott</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>&gt;201</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>≤153</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>154-177</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>178-201</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>&gt;201</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>≤153</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>154-177</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>178-201</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>&gt;201</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CORRIDOR (dédoublonné)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>≤153</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CORRIDOR (dédoublonné)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>154-177</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CORRIDOR (dédoublonné)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>178-201</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>base_cap160</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CORRIDOR (dédoublonné)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>&gt;201</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>MTL-QC</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>≤153</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>MTL-QC</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>154-177</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>MTL-QC</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>178-201</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>MTL-QC</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>&gt;201</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MTL-Ott</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>≤153</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>MTL-Ott</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>154-177</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>MTL-Ott</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>178-201</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>MTL-Ott</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>&gt;201</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>≤153</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>154-177</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>178-201</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>&gt;201</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>≤153</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>154-177</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>178-201</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>&gt;201</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CORRIDOR (dédoublonné)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>≤153</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CORRIDOR (dédoublonné)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>154-177</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CORRIDOR (dédoublonné)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>178-201</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>recommande_cap177</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CORRIDOR (dédoublonné)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>&gt;201</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D61"/>
+  <autoFilter ref="A1:D101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/livrables/passages_niveau_par_bande.xlsx
+++ b/livrables/passages_niveau_par_bande.xlsx
@@ -430,7 +430,7 @@
   <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -461,7 +461,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -501,7 +501,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -581,7 +581,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -641,7 +641,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -681,7 +681,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -701,7 +701,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>geometrie-base</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -881,7 +881,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -921,7 +921,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1061,7 +1061,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1121,7 +1121,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1161,7 +1161,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1181,7 +1181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1221,7 +1221,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>geometrie-recommande</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1301,7 +1301,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1341,7 +1341,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1361,7 +1361,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1461,7 +1461,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1481,7 +1481,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1501,7 +1501,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1561,7 +1561,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1581,7 +1581,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1601,7 +1601,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>geometrie-reference-interne</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1821,7 +1821,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1841,7 +1841,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1881,7 +1881,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1901,7 +1901,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1921,7 +1921,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1961,7 +1961,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2001,7 +2001,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2021,7 +2021,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2041,7 +2041,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>base_cap160</t>
+          <t>exploitation-base (cap 160)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2081,7 +2081,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2101,7 +2101,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2121,7 +2121,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2221,7 +2221,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2241,7 +2241,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2281,7 +2281,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2321,7 +2321,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2361,7 +2361,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2381,7 +2381,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2401,7 +2401,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2421,7 +2421,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2441,7 +2441,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>recommande_cap177</t>
+          <t>exploitation-recommande (cap 177)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">

--- a/livrables/passages_niveau_par_bande.xlsx
+++ b/livrables/passages_niveau_par_bande.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>195</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>127</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21">
@@ -861,7 +861,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -875,13 +875,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -895,13 +895,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>228</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -955,13 +955,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1035,13 +1035,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1055,13 +1055,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1075,13 +1075,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>254</v>
+        <v>236</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>330</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>33</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1215,13 +1215,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>geometrie-recommande</t>
+          <t>geometrie-pendulaire</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>672</v>
+        <v>627</v>
       </c>
     </row>
     <row r="42">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45">
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>249</v>
+        <v>230</v>
       </c>
     </row>
     <row r="46">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>293</v>
+        <v>268</v>
       </c>
     </row>
     <row r="54">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>361</v>
+        <v>333</v>
       </c>
     </row>
     <row r="58">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="61">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="62">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>245</v>
+        <v>230</v>
       </c>
     </row>
     <row r="64">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="67">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>291</v>
+        <v>266</v>
       </c>
     </row>
     <row r="72">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="75">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>361</v>
+        <v>329</v>
       </c>
     </row>
     <row r="76">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>195</v>
+        <v>252</v>
       </c>
     </row>
     <row r="79">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>729</v>
+        <v>672</v>
       </c>
     </row>
     <row r="80">
@@ -2061,7 +2061,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>309</v>
+        <v>289</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2121,7 +2121,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>194</v>
+        <v>180</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2221,7 +2221,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2235,13 +2235,13 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>295</v>
+        <v>276</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2281,7 +2281,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2335,13 +2335,13 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>364</v>
+        <v>340</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2361,7 +2361,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2381,7 +2381,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>33</v>
+        <v>91</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2415,13 +2415,13 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>891</v>
+        <v>833</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2441,7 +2441,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>exploitation-recommande (cap 177)</t>
+          <t>exploitation-pendulaire (cap 177)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">

--- a/livrables/passages_niveau_par_bande.xlsx
+++ b/livrables/passages_niveau_par_bande.xlsx
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>289</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84">
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
     </row>
     <row r="85">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>180</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>276</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="93">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>340</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="97">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>833</v>
+        <v>161</v>
       </c>
     </row>
     <row r="100">
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>672</v>
       </c>
     </row>
     <row r="101">
